--- a/用卷/2002.xlsx
+++ b/用卷/2002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\高考用卷\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC32AE5E-D78D-4877-983C-04ACB3679ECC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44E39426-A355-4774-A463-FC650107ADE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -391,37 +391,37 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -707,11 +707,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
       <c r="D1" s="7"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -750,7 +750,7 @@
       <c r="C4" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="D4" s="15"/>
+      <c r="D4" s="20"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
@@ -762,7 +762,7 @@
       <c r="C5" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D5" s="15"/>
+      <c r="D5" s="20"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
@@ -869,10 +869,10 @@
       <c r="B14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="D14" s="16"/>
+      <c r="D14" s="17"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
@@ -881,8 +881,8 @@
       <c r="B15" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="12"/>
-      <c r="D15" s="17"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="18"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
@@ -930,7 +930,7 @@
       <c r="C19" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="D19" s="18"/>
+      <c r="D19" s="11"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
@@ -1002,7 +1002,7 @@
       <c r="C25" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="D25" s="19"/>
+      <c r="D25" s="12"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
@@ -1014,7 +1014,7 @@
       <c r="C26" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="D26" s="19"/>
+      <c r="D26" s="12"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
@@ -1062,7 +1062,7 @@
       <c r="C30" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="D30" s="20"/>
+      <c r="D30" s="13"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
@@ -1151,17 +1151,17 @@
       <c r="D37" s="10"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="21"/>
-      <c r="B38" s="21"/>
+      <c r="A38" s="14"/>
+      <c r="B38" s="14"/>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="13" t="s">
+      <c r="A39" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="B39" s="13"/>
-      <c r="C39" s="13"/>
+      <c r="B39" s="19"/>
+      <c r="C39" s="19"/>
       <c r="D39" s="8"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
